--- a/revision_v3/human_eval/Pilot_Code_Review.xlsx
+++ b/revision_v3/human_eval/Pilot_Code_Review.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +44,13 @@
       <name val="Consolas"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +81,16 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1FA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -89,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -125,6 +140,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -709,6 +730,15 @@
     <col width="48" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="48" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="80" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="80" customWidth="1" min="31" max="31"/>
+    <col width="80" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="33" max="33"/>
+    <col width="50" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -840,6 +870,51 @@
       <c r="Z1" s="5" t="inlineStr">
         <is>
           <t>final_reason</t>
+        </is>
+      </c>
+      <c r="AA1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_proposed_label</t>
+        </is>
+      </c>
+      <c r="AB1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_confidence</t>
+        </is>
+      </c>
+      <c r="AC1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_rationale</t>
+        </is>
+      </c>
+      <c r="AD1" s="11" t="inlineStr">
+        <is>
+          <t>source_static_analyzer_verdict</t>
+        </is>
+      </c>
+      <c r="AE1" s="11" t="inlineStr">
+        <is>
+          <t>source_static_analyzer_explanation</t>
+        </is>
+      </c>
+      <c r="AF1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_relevant_code_summary</t>
+        </is>
+      </c>
+      <c r="AG1" s="11" t="inlineStr">
+        <is>
+          <t>guard_tracer_result</t>
+        </is>
+      </c>
+      <c r="AH1" s="11" t="inlineStr">
+        <is>
+          <t>project_and_onchain_evidence</t>
+        </is>
+      </c>
+      <c r="AI1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_unresolved_questions</t>
         </is>
       </c>
     </row>
@@ -954,6 +1029,60 @@
       <c r="X2" s="6" t="inlineStr"/>
       <c r="Y2" s="8" t="inlineStr"/>
       <c r="Z2" s="8" t="inlineStr"/>
+      <c r="AA2" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AB2" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC2" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [944]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD2" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE2" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF2" s="12" t="inlineStr">
+        <is>
+          <t>960-byte runtime on optimism exposing 3 dispatched function(s): 0x4576d251, 0x7fb74289, 0xb9635e63
+Instruction census (whole contract): CALL×3, CALLER×4, ORIGIN×3</t>
+        </is>
+      </c>
+      <c r="AG2" s="12" t="inlineStr">
+        <is>
+          <t>• 0x4576d251: no sensitive operation reachable
+• 0x7fb74289: an unauthenticated path to a sensitive operation exists
+• 0xb9635e63: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH2" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=960 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+addresses embedded in the code: [{"bytecode_offset": 68, "address": "0x88adce4c2acb8d0e047f4135ff0d313dd4972552"}]</t>
+        </is>
+      </c>
+      <c r="AI2" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [944]}) — capability here is a lower bound; unauthenticated call(s) forwarding only msg.value to a fixed destination ([('0x7fb74289', 545, '0x88adce4c2acb8d0e047f4135ff0d313dd4972552')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -1066,6 +1195,58 @@
       <c r="X3" s="9" t="inlineStr"/>
       <c r="Y3" s="8" t="inlineStr"/>
       <c r="Z3" s="8" t="inlineStr"/>
+      <c r="AA3" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB3" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC3" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate. MANUAL REVIEW OVERRIDE: Confidence lowered from HIGH to MEDIUM. The finding stands — an unauthenticated setup(...) that writes storage slot 0 and then DELEGATECALLs, on an account whose storage is empty at authorization time, lets whichever party calls first establish the account's configuration — but the analyser resolved the SSTORE's value from storage rather than from calldata, so exactly which authority the first caller installs was not established from the bytecode alone. The hazard class is certain; its precise mechanics are not.</t>
+        </is>
+      </c>
+      <c r="AD3" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE3" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF3" s="12" t="inlineStr">
+        <is>
+          <t>889-byte runtime on polygon exposing 1 dispatched function(s): setup(address[],uint256,address,bytes,address,address,uint256,address)
+Concern(s) found: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage; setup(address[],uint256,address,bytes,address,address,uint256,address): SSTORE to slot 0x0 at pc=421 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'DELEGATECALL': 2, 'SSTORE': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — DELEGATECALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): DELEGATECALL×2, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AG3" s="12" t="inlineStr">
+        <is>
+          <t>• setup(address[],uint256,address,bytes,address,address,uint256,address): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AH3" s="12" t="inlineStr">
+        <is>
+          <t>chain=polygon
+runtime size=889 bytes
+verified source=False
+other chains with identical bytecode: ["polygon"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 0, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AI3" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1178,6 +1359,60 @@
       <c r="X4" s="6" t="inlineStr"/>
       <c r="Y4" s="8" t="inlineStr"/>
       <c r="Z4" s="8" t="inlineStr"/>
+      <c r="AA4" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB4" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: forward(address,bytes): msg.sender must equal the hardcoded address 0xe51504ffee530eaf61f6af654793ce459ff98833. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate. MANUAL REVIEW OVERRIDE: Confidence raised from LOW to MEDIUM. The single entry point forward(address,bytes) is fully analysed with no coverage gap, and its only guard compares msg.sender against the hardcoded literal 0xe51504ffee530eaf61f6af654793ce459ff98833 (embedded at bytecode offset 186, with the revert string 'RestrictedRouter: unauthorized'). Under EIP-7702 that literal cannot be the authorizing EOA, so it names a fixed third party who can make the account issue calls to targets and with payloads of their choosing. The previous pass read the same guard as evidence of safety; that reading is correct for an ordinary contract and wrong for a delegate.</t>
+        </is>
+      </c>
+      <c r="AD4" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE4" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AF4" s="12" t="inlineStr">
+        <is>
+          <t>1304-byte runtime on base exposing 2 dispatched function(s): forward(address,bytes), 0xd5f768bf Embedded strings mention: Router, unauthorized.
+Concern(s) found: forward(address,bytes): msg.sender must equal the hardcoded address 0xe51504ffee530eaf61f6af654793ce459ff98833. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×2, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AG4" s="12" t="inlineStr">
+        <is>
+          <t>• forward(address,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xe51504ffee530eaf61f6af654793ce459ff98833
+• 0xd5f768bf: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH4" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1304 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+addresses embedded in the code: [{"bytecode_offset": 186, "address": "0xe51504ffee530eaf61f6af654793ce459ff98833"}]</t>
+        </is>
+      </c>
+      <c r="AI4" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1265]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1290,6 +1525,70 @@
       <c r="X5" s="9" t="inlineStr"/>
       <c r="Y5" s="8" t="inlineStr"/>
       <c r="Z5" s="8" t="inlineStr"/>
+      <c r="AA5" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AB5" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC5" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2123, 2247]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD5" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE5" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AF5" s="12" t="inlineStr">
+        <is>
+          <t>8345-byte runtime on ethereum exposing 12 dispatched function(s): coin(), 0x37a25dc2, burn(), renounceOwnership(), 0x7470445f, owner(), initialize(address,address[]), 0xba49f371, 0xc4a805ee, transferOwnership(address) Embedded strings mention: Ownable.
+Protection(s) found: msg.sender compared against a stored authority on 0x37a25dc2, 0x7470445f, 0xba49f371, 0xc4a805ee, burn(), drain(uint256)
+Instruction census (whole contract): ADDRESS×13, CALL×8, CALLER×3, ORIGIN×1, SSTORE×8, STATICCALL×6</t>
+        </is>
+      </c>
+      <c r="AG5" s="12" t="inlineStr">
+        <is>
+          <t>• coin(): no sensitive operation reachable
+• 0x37a25dc2: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• burn(): no sensitive operation reachable — check found: storage_based_caller_check; storage_based_caller_check
+• renounceOwnership(): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• 0x7470445f: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• owner(): no sensitive operation reachable
+• initialize(address,address[]): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• 0xba49f371: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• 0xc4a805ee: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• transferOwnership(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• drain(uint256): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• dust(): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH5" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=8345 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 11, "n_writes": 2}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 4, "n_writes": 1}, {"slot": "0000000000</t>
+        </is>
+      </c>
+      <c r="AI5" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2123, 2247]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1402,6 +1701,76 @@
       <c r="X6" s="6" t="inlineStr"/>
       <c r="Y6" s="8" t="inlineStr"/>
       <c r="Z6" s="8" t="inlineStr"/>
+      <c r="AA6" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AB6" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC6" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2161]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate. MANUAL REVIEW OVERRIDE: The framework's UNSAFE rested on a calldata-derived call target attributed to 0x2f15f5fc, whose declared argument list is a single uint256 — a shape that cannot plausibly carry an arbitrary call target. This is a 15,226-byte contract with 19 dispatched functions where the traversal hit its exploration cap on eight of them and one CALL site was never reached at all, so the provenance behind that finding is not trustworthy. No concrete unauthenticated path is established, and no positive authorization control is confirmed either.</t>
+        </is>
+      </c>
+      <c r="AD6" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE6" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF6" s="12" t="inlineStr">
+        <is>
+          <t>15226-byte runtime on base exposing 19 dispatched function(s): 0x00b16584, supportsInterface(bytes4), 0x299ed167, 0x2ab11a7a, 0x2f15f5fc, 0x533c1273, 0x5817ebe4, 0x762d0698, 0x7b6eb5f4, getUnsafeDepositId(address,bytes32,uint256)
+Concern(s) found: 0x2f15f5fc: CALL at pc=4326 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x2f15f5fc: CALL at pc=15042 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x2f15f5fc: CALL at pc=15115 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x2f15f5fc: CALL at pc=15130 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x00b16584: msg.sender must equal the hardcoded address 0xb3fcb766efa166492522e4861c9f84a147b09eaf. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xfe02e33d: msg.sender must equal the hardcoded address 0xb3fcb766efa166492522e4861c9f84a147b09eaf. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×5, CALL×12, CALLER×3, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AG6" s="12" t="inlineStr">
+        <is>
+          <t>• 0x00b16584: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xb3fcb766efa166492522e4861c9f84a147b09eaf [analysis incomplete for this function]
+• supportsInterface(bytes4): no sensitive operation reachable
+• 0x299ed167: no sensitive operation reachable [analysis incomplete for this function]
+• 0x2ab11a7a: no sensitive operation reachable [analysis incomplete for this function]
+• 0x2f15f5fc: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• 0x533c1273: no sensitive operation reachable [analysis incomplete for this function]
+• 0x5817ebe4: no sensitive operation reachable
+• 0x762d0698: no sensitive operation reachable [analysis incomplete for this function]
+• 0x7b6eb5f4: no sensitive operation reachable
+• getUnsafeDepositId(address,bytes32,uint256): no sensitive operation reachable
+• 0x853c3f38: no sensitive operation reachable
+• ARBITER(): no sensitive operation reachable
+• 0x98e4439a: no sensitive operation reachable
+• 0x98f52ce5: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• 0xb1bb5bc1: no sensitive operation reachable
+• 0xc6445e16: no sensitive operation reachable [analysis incomplete for this function]
+• 0xc85d92c2: no sensitive operation reachable
+• 0xd5e961d6: no sensitive operation reachable
+• 0xfe02e33d: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xb3fcb766efa166492522e4861c9f84a147b09eaf [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH6" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=15226 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AI6" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2161]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x00b16584, 0x299ed167, 0x2ab11a7a, 0x2f15f5fc, 0x533c1273, 0x762d0698, 0x98f52ce5, 0xc6445e16; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x2f15f5fc pc=4843 -&gt; 0x09aea4b2242abc8bb4bb78d537a67a245a7bec64 (value=0, data=memory); 0x98f52ce5 pc=2602 -&gt; 0x041d8cf89e71a6ae4f86084e717a6de102eca53a (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -1514,6 +1883,57 @@
       <c r="X7" s="9" t="inlineStr"/>
       <c r="Y7" s="8" t="inlineStr"/>
       <c r="Z7" s="8" t="inlineStr"/>
+      <c r="AA7" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB7" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC7" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x040113fc: tx.origin must equal the hardcoded address 0x9dcb4cd97a2e871834659fee2c837d2432c54caa. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD7" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE7" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF7" s="12" t="inlineStr">
+        <is>
+          <t>1937-byte runtime on base exposing 1 dispatched function(s): 0x040113fc Embedded strings mention: Not owner.
+Concern(s) found: 0x040113fc: tx.origin must equal the hardcoded address 0x9dcb4cd97a2e871834659fee2c837d2432c54caa. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×2, ORIGIN×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AG7" s="12" t="inlineStr">
+        <is>
+          <t>• 0x040113fc: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x9dcb4cd97a2e871834659fee2c837d2432c54caa</t>
+        </is>
+      </c>
+      <c r="AH7" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1937 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AI7" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1626,6 +2046,63 @@
       <c r="X8" s="6" t="inlineStr"/>
       <c r="Y8" s="8" t="inlineStr"/>
       <c r="Z8" s="8" t="inlineStr"/>
+      <c r="AA8" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB8" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AC8" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: transferTokens(address): CALL at pc=1953 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD8" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE8" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF8" s="12" t="inlineStr">
+        <is>
+          <t>4870-byte runtime on base exposing 4 dispatched function(s): transferTokens(address), 0x29cd3d04, 0x535089e7, executeCall(address,bytes) Embedded strings mention: ReentrancyGuard, Signed Message.
+Concern(s) found: transferTokens(address): CALL at pc=1953 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; executeCall(address,bytes): CALL at pc=2420 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; transferTokens(address): SSTORE to slot 0x0 at pc=589 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; transferTokens(address): SSTORE to slot 0x0 at pc=630 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x29cd3d04: SSTORE to slot 0x0 at pc=735 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x29cd3d04: SSTORE to slot 0x0 at pc=767 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; 0x535089e7: SSTORE to slot 0x0 at pc=871 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; executeCall(address,bytes): SSTORE to slot 0x0 at pc=1504 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; executeCall(address,bytes): SSTORE to slot 0x0 at pc=1547 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0x535089e7
+Instruction census (whole contract): ADDRESS×1, CALL×5, SSTORE×8, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AG8" s="12" t="inlineStr">
+        <is>
+          <t>• transferTokens(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x29cd3d04: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x535089e7: an unauthenticated path to a sensitive operation exists — check found: storage_condition; signature_authorization
+• executeCall(address,bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH8" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=4870 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint8", "n_reads": 4, "n_writes": 4}]</t>
+        </is>
+      </c>
+      <c r="AI8" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [4827]}) — capability here is a lower bound; unauthenticated call(s) forwarding only msg.value to a fixed destination ([('transferTokens(address)', 370, '0xd0e49dec126d0ac848389843917c5204aa2be5c2'), ('0x29cd3d04', 370, '0xd0e49dec126d0ac848389843917c5204aa2be5c2'), ('executeCall(address,bytes)', 370, '0xd0e49dec126d0ac848389843917c5204aa2be5c2')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -1738,6 +2215,58 @@
       <c r="X9" s="9" t="inlineStr"/>
       <c r="Y9" s="8" t="inlineStr"/>
       <c r="Z9" s="8" t="inlineStr"/>
+      <c r="AA9" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB9" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC9" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: start(address[],uint256[]): msg.sender must equal the hardcoded address 0xbb7218d77f06a89c15e9188b1f1b427ae8f0290c. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD9" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE9" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF9" s="12" t="inlineStr">
+        <is>
+          <t>2352-byte runtime on bnb exposing 1 dispatched function(s): start(address[],uint256[])
+Concern(s) found: start(address[],uint256[]): msg.sender must equal the hardcoded address 0xbb7218d77f06a89c15e9188b1f1b427ae8f0290c. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×3, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AG9" s="12" t="inlineStr">
+        <is>
+          <t>• start(address[],uint256[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xbb7218d77f06a89c15e9188b1f1b427ae8f0290c [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AH9" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=2352 bytes
+verified source=False
+other chains with identical bytecode: ["bnb", "ethereum", "optimism"]
+addresses embedded in the code: [{"bytecode_offset": 40, "address": "0xbb7218d77f06a89c15e9188b1f1b427ae8f0290c"}]</t>
+        </is>
+      </c>
+      <c r="AI9" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: start(address[],uint256[])</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1850,6 +2379,60 @@
       <c r="X10" s="6" t="inlineStr"/>
       <c r="Y10" s="8" t="inlineStr"/>
       <c r="Z10" s="8" t="inlineStr"/>
+      <c r="AA10" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB10" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AC10" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0xcf641220: CALL at pc=983 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD10" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE10" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF10" s="12" t="inlineStr">
+        <is>
+          <t>3397-byte runtime on ethereum exposing 2 dispatched function(s): destination(), 0xcf641220
+Concern(s) found: 0xcf641220: CALL at pc=983 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 3, 'SSTORE': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx3 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×3, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AG10" s="12" t="inlineStr">
+        <is>
+          <t>• destination(): no sensitive operation reachable
+• 0xcf641220: an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH10" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3397 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AI10" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [3369]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1962,6 +2545,60 @@
       <c r="X11" s="9" t="inlineStr"/>
       <c r="Y11" s="8" t="inlineStr"/>
       <c r="Z11" s="8" t="inlineStr"/>
+      <c r="AA11" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB11" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AC11" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x04f3a55d: msg.sender must equal the hardcoded address 0xe039802366498c5cc75b200decaa9ad520e60a11. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD11" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE11" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF11" s="12" t="inlineStr">
+        <is>
+          <t>3497-byte runtime on gnosis exposing 3 dispatched function(s): 0x04f3a55d, 0x773d5602, owner() Embedded strings mention: Executor, not authorized.
+Concern(s) found: 0x04f3a55d: msg.sender must equal the hardcoded address 0xe039802366498c5cc75b200decaa9ad520e60a11. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0x04f3a55d: msg.sender must equal the hardcoded address 0xe039802366498c5cc75b200decaa9ad520e60a11. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×5, CALLER×3</t>
+        </is>
+      </c>
+      <c r="AG11" s="12" t="inlineStr">
+        <is>
+          <t>• 0x04f3a55d: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xe039802366498c5cc75b200decaa9ad520e60a11; hardcoded_address_check against 0xe039802366498c5cc75b200decaa9ad520e60a11
+• 0x773d5602: no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH11" s="12" t="inlineStr">
+        <is>
+          <t>chain=gnosis
+runtime size=3497 bytes
+verified source=False
+other chains with identical bytecode: ["gnosis"]</t>
+        </is>
+      </c>
+      <c r="AI11" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [3482]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2074,6 +2711,59 @@
       <c r="X12" s="6" t="inlineStr"/>
       <c r="Y12" s="8" t="inlineStr"/>
       <c r="Z12" s="8" t="inlineStr"/>
+      <c r="AA12" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB12" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AC12" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: destroyMe(): tx.origin must equal the hardcoded address 0x6511204da888f103156fe67980d27bc8307981e8. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD12" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE12" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF12" s="12" t="inlineStr">
+        <is>
+          <t>2900-byte runtime on base exposing 2 dispatched function(s): 0x0a7c8ed6, destroyMe() Embedded strings mention: Multicall, not owner.
+Concern(s) found: destroyMe(): tx.origin must equal the hardcoded address 0x6511204da888f103156fe67980d27bc8307981e8. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×3, CALLER×1, ORIGIN×2, SELFDESTRUCT×2, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AG12" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0a7c8ed6: no sensitive operation reachable — check found: hardcoded_address_check against 0x6511204da888f103156fe67980d27bc8307981e8 [analysis incomplete for this function]
+• destroyMe(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x6511204da888f103156fe67980d27bc8307981e8
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH12" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2900 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AI12" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [731], 'SELFDESTRUCT': [2857]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x0a7c8ed6</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -2186,6 +2876,66 @@
       <c r="X13" s="9" t="inlineStr"/>
       <c r="Y13" s="8" t="inlineStr"/>
       <c r="Z13" s="8" t="inlineStr"/>
+      <c r="AA13" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB13" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AC13" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: forwardCall(address,uint256,bytes): msg.sender must equal the hardcoded address 0x1764890fee523e0aa4f464dba43e520b3a50e3d7. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD13" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE13" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF13" s="12" t="inlineStr">
+        <is>
+          <t>5405-byte runtime on base exposing 8 dispatched function(s): transferERC721(address,address,uint256), recipient(), forwardCall(address,uint256,bytes), owner(), transferERC1155(address,address,uint256,uint256,bytes), sweepERC20(address), transferERC20(address,uint256), 0xfaa0f4d8
+Concern(s) found: forwardCall(address,uint256,bytes): msg.sender must equal the hardcoded address 0x1764890fee523e0aa4f464dba43e520b3a50e3d7. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; sweepERC20(address): msg.sender must equal the hardcoded address 0x1764890fee523e0aa4f464dba43e520b3a50e3d7. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; transferERC20(address,uint256): msg.sender must equal the hardcoded address 0x1764890fee523e0aa4f464dba43e520b3a50e3d7. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×2, CALL×8, CALLER×7, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AG13" s="12" t="inlineStr">
+        <is>
+          <t>• transferERC721(address,address,uint256): no sensitive operation reachable
+• recipient(): no sensitive operation reachable
+• forwardCall(address,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x1764890fee523e0aa4f464dba43e520b3a50e3d7 [analysis incomplete for this function]
+• owner(): no sensitive operation reachable
+• transferERC1155(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• sweepERC20(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x1764890fee523e0aa4f464dba43e520b3a50e3d7
+• transferERC20(address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x1764890fee523e0aa4f464dba43e520b3a50e3d7
+• 0xfaa0f4d8: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH13" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=5405 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+addresses embedded in the code: [{"bytecode_offset": 499, "address": "0x836d416742f15e816c4bf98e63663e32c814b47d"}, {"bytecode_offset": 690, "address": "0x1764890fee523e0aa4f464dba43e520b3a50e3d7"}]</t>
+        </is>
+      </c>
+      <c r="AI13" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [926, 1560, 2591, 2925]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: forwardCall(address,uint256,bytes)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2298,6 +3048,58 @@
       <c r="X14" s="6" t="inlineStr"/>
       <c r="Y14" s="8" t="inlineStr"/>
       <c r="Z14" s="8" t="inlineStr"/>
+      <c r="AA14" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB14" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC14" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate. MANUAL REVIEW OVERRIDE: Same bytecode family and same finding as the Polygon item above (identical delegatecall target 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab); confidence lowered to MEDIUM for the same reason.</t>
+        </is>
+      </c>
+      <c r="AD14" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE14" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AF14" s="12" t="inlineStr">
+        <is>
+          <t>889-byte runtime on optimism exposing 1 dispatched function(s): setup(address[],uint256,address,bytes,address,address,uint256,address)
+Concern(s) found: setup(address[],uint256,address,bytes,address,address,uint256,address): DELEGATECALL at pc=435 to 0xcfaa26ad40bfc7e3b1642e1888620fc402b95dab reachable with no authorization branch — third-party code would execute against the EOA's own storage; setup(address[],uint256,address,bytes,address,address,uint256,address): SSTORE to slot 0x0 at pc=421 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'DELEGATECALL': 2, 'SSTORE': 1, 'STATICCALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — DELEGATECALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): DELEGATECALL×2, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AG14" s="12" t="inlineStr">
+        <is>
+          <t>• setup(address[],uint256,address,bytes,address,address,uint256,address): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AH14" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=889 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 0, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AI14" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -2410,6 +3212,58 @@
       <c r="X15" s="9" t="inlineStr"/>
       <c r="Y15" s="8" t="inlineStr"/>
       <c r="Z15" s="8" t="inlineStr"/>
+      <c r="AA15" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AB15" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC15" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on execute((address,uint256,bytes)[]) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD15" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE15" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AF15" s="12" t="inlineStr">
+        <is>
+          <t>2043-byte runtime on bnb exposing 1 dispatched function(s): execute((address,uint256,bytes)[])
+Protection(s) found: self-call restriction (msg.sender == address(this)) on execute((address,uint256,bytes)[]) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×3</t>
+        </is>
+      </c>
+      <c r="AG15" s="12" t="inlineStr">
+        <is>
+          <t>• execute((address,uint256,bytes)[]): every path to a sensitive operation passes an authorization check — check found: self_call_check; self_call_check [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AH15" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=2043 bytes
+verified source=False
+other chains with identical bytecode: ["bnb", "ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 124, "address": "0xed7c5fefe0790db355b0316f41269006ecd87653"}]</t>
+        </is>
+      </c>
+      <c r="AI15" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: execute((address,uint256,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -2522,6 +3376,58 @@
       <c r="X16" s="6" t="inlineStr"/>
       <c r="Y16" s="8" t="inlineStr"/>
       <c r="Z16" s="8" t="inlineStr"/>
+      <c r="AA16" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB16" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AC16" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=214 to 0xa8204582fe8f915b7f423b1450b654fc98ff921d with value from calldata, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD16" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AE16" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AF16" s="12" t="inlineStr">
+        <is>
+          <t>466-byte runtime on bnb exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=214 to 0xa8204582fe8f915b7f423b1450b654fc98ff921d with value from calldata, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 6, 'ADDRESS': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx6 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): ADDRESS×1, CALL×6</t>
+        </is>
+      </c>
+      <c r="AG16" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AH16" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=466 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 54, "address": "0xa8204582fe8f915b7f423b1450b654fc98ff9200"}]</t>
+        </is>
+      </c>
+      <c r="AI16" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: &lt;no dispatcher recovered; analysed from pc=0&gt;; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: &lt;no dispatcher recovered; analysed from pc=0&gt; pc=171 -&gt; calldata-derived target (value=unresolved, argument provenance unreliable: the stack model was padded for this function); &lt;no dispatcher recovered; analysed from pc=0&gt; pc=315 -&gt; calldata-derived target (value=unresolved, argument provenance unreliable: the stack model was padded for this function); &lt;no dispatcher recovered; analysed from pc=0&gt; pc=351 -&gt; calldata-derived target (value=unresolved, argument provenance unreliable: the stack model was padded for this function); &lt;no dispatcher recovered; analysed from pc=0&gt; pc=442 -&gt; calldata-derived target (value=unresolved, argument provenance unreliable: the stack model was padded for this function). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.; unauthenticated call(s) forwarding only msg.value to a fixed destination ([('&lt;no dispatcher recovered; analysed from pc=0&gt;', 79, '0xa8204582fe8f915b7f423b1450b654fc98ff921d')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -2634,6 +3540,57 @@
       <c r="X17" s="9" t="inlineStr"/>
       <c r="Y17" s="8" t="inlineStr"/>
       <c r="Z17" s="8" t="inlineStr"/>
+      <c r="AA17" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AB17" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC17" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [598], 'CREATE2': [3142]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD17" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE17" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AF17" s="12" t="inlineStr">
+        <is>
+          <t>3165-byte runtime on base exposing 1 dispatched function(s): 0xcb3a0d5c
+Instruction census (whole contract): CALL×1, CALLER×1, CREATE2×1, STATICCALL×3</t>
+        </is>
+      </c>
+      <c r="AG17" s="12" t="inlineStr">
+        <is>
+          <t>• 0xcb3a0d5c: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH17" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=3165 bytes
+verified source=False
+other chains with identical bytecode: ["base", "bnb"]</t>
+        </is>
+      </c>
+      <c r="AI17" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [598], 'CREATE2': [3142]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2746,6 +3703,87 @@
       <c r="X18" s="6" t="inlineStr"/>
       <c r="Y18" s="8" t="inlineStr"/>
       <c r="Z18" s="8" t="inlineStr"/>
+      <c r="AA18" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB18" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC18" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: routeClaim(bytes,bytes): DELEGATECALL at pc=9554 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD18" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE18" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AF18" s="12" t="inlineStr">
+        <is>
+          <t>9874-byte runtime on optimism exposing 28 dispatched function(s): supportsInterface(bytes4), 0x0c6c9f35, 0x0cfc0c3c, 0x12b19afd, setAtomicFillSigner(address), initialized(), getRoleAdmin(bytes32), grantRole(bytes32,address), DOMAIN_SEPARATOR(), renounceRole(bytes32,address) Embedded strings mention: Router, Signed Message.
+Concern(s) found: routeClaim(bytes,bytes): DELEGATECALL at pc=9554 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; 0x811ef45c: DELEGATECALL at pc=9554 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; 0xdf2c9057: DELEGATECALL at pc=9554 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage
+Protection(s) found: self-call restriction (msg.sender == address(this)) on initialize(address) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on 0x811ef45c, 0xdf2c9057
+Instruction census (whole contract): ADDRESS×8, CALL×3, CALLER×15, DELEGATECALL×1, SSTORE×15, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AG18" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• 0x0c6c9f35: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• 0x0cfc0c3c: no sensitive operation reachable
+• 0x12b19afd: an unauthenticated path to a sensitive operation exists
+• setAtomicFillSigner(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• initialized(): no sensitive operation reachable
+• getRoleAdmin(bytes32): no sensitive operation reachable
+• grantRole(bytes32,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• DOMAIN_SEPARATOR(): no sensitive operation reachable
+• renounceRole(bytes32,address): every path to a sensitive operation passes an authorization check — check found: calldata_comparison; storage_condition
+• 0x45197d6b: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• initialize(address,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• routeClaim(bytes,bytes): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0x811ef45c: an unauthenticated path to a sensitive operation exists — check found: storage_condition; signature_authorization [analysis incomplete for this function]
+• pause(): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• eip712Domain(): no sensitive operation reachable [analysis incomplete for this function]
+• hasRole(bytes32,address): no sensitive operation reachable
+• 0x925230b0: no sensitive operation reachable
+• DEFAULT_ADMIN_ROLE(): no sensitive operation reachable
+• 0xb51d6fdf: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0xb72ff04f: no sensitive operation reachable
+• initialize(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xd1dcdd8e6fe04c338ac3f76f7d7105becab74f77; self_call_check
+• 0xcfbf97b6: no sensitive operation reachable
+• 0xcfd4bf49: no sensitive operation reachable
+• revokeRole(bytes32,address): an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0xdf2c9057: an unauthenticated path to a sensitive operation exists — check found: storage_condition; signature_authorization [analysis incomplete for this function]
+• 0xdffffc34: no sensitive operation reachable
+• 0xf7101677: an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AH18" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=9874 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "1ec626b893ca4a4a01eaf39ec7e7bd14742f8b05d0ff7a16b9587dccde396f2c", "offset": 0, "type": "mapping(address =&gt; uint8)", "n_reads": 4, "n_writes": 2}, {"slot": "32082cf48e80a36a6bd2e8ae64f9fbe0be581fd2c37c677bd828491c7122bcf0", "offset": 0, "type": "uint8", "n_reads": 1, "n_writes": 1}, {"slo
+addresses embedded in the code: [{"bytecode_offset": 2165, "address": "0xd1dcdd8e6fe04c338ac3f76f7d7105becab74f77"}]</t>
+        </is>
+      </c>
+      <c r="AI18" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: renounceRole(bytes32,address) (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x811ef45c, 0xdf2c9057, eip712Domain(); unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x12b19afd pc=7227 -&gt; 0x2e1c12e70e9a0cf9e62e2904baa8d732a8c12a53 (value=0, data=memory); 0x811ef45c pc=4334 -&gt; 0x3b1e31dd618afbe87e3109f31f5735213ac92d2c (value=0, data=memory); 0x811ef45c pc=7227 -&gt; 0x2e1c12e70e9a0cf9e62e2904baa8d732a8c12a53 (value=0, data=memory); 0xdf2c9057 pc=1285 -&gt; 0x3b1e31dd618afbe87e3109f31f5735213ac92d2c (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -2858,6 +3896,57 @@
       <c r="X19" s="9" t="inlineStr"/>
       <c r="Y19" s="8" t="inlineStr"/>
       <c r="Z19" s="8" t="inlineStr"/>
+      <c r="AA19" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AB19" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC19" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [309]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD19" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE19" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AF19" s="12" t="inlineStr">
+        <is>
+          <t>2715-byte runtime on arbitrum exposing 1 dispatched function(s): executeBatch((address,uint256,bytes)[]) Embedded strings mention: BatchDelegator.
+Instruction census (whole contract): CALL×1, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AG19" s="12" t="inlineStr">
+        <is>
+          <t>• executeBatch((address,uint256,bytes)[]): no sensitive operation reachable [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH19" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=2715 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]</t>
+        </is>
+      </c>
+      <c r="AI19" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [309]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: executeBatch((address,uint256,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2970,6 +4059,61 @@
       <c r="X20" s="6" t="inlineStr"/>
       <c r="Y20" s="8" t="inlineStr"/>
       <c r="Z20" s="8" t="inlineStr"/>
+      <c r="AA20" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AB20" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AC20" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: forwardCall(address,uint256,bytes): CALL at pc=266 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AD20" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AE20" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AF20" s="12" t="inlineStr">
+        <is>
+          <t>2250-byte runtime on ethereum exposing 4 dispatched function(s): forwardCall(address,uint256,bytes), transferERC721(address,address,address,uint256), transferERC20(address,address,uint256), transferERC1155(address,address,address,uint256,uint256,bytes)
+Concern(s) found: forwardCall(address,uint256,bytes): CALL at pc=266 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 5}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx5 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×5</t>
+        </is>
+      </c>
+      <c r="AG20" s="12" t="inlineStr">
+        <is>
+          <t>• forwardCall(address,uint256,bytes): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• transferERC721(address,address,address,uint256): no sensitive operation reachable
+• transferERC20(address,address,uint256): no sensitive operation reachable
+• transferERC1155(address,address,address,uint256,uint256,bytes): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AH20" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2250 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AI20" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [486, 583, 733, 2215]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: forwardCall(address,uint256,bytes)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -3082,6 +4226,57 @@
       <c r="X21" s="9" t="inlineStr"/>
       <c r="Y21" s="8" t="inlineStr"/>
       <c r="Z21" s="8" t="inlineStr"/>
+      <c r="AA21" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AB21" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AC21" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate. MANUAL REVIEW OVERRIDE: 166 bytes, one code path, one capability: forward msg.value to the address in storage slot 0. No path anywhere in the runtime writes slot 0, and under EIP-7702 the slot read is the AUTHORIZING EOA's own slot 0, which is empty — so the destination is address(0) and the only value moved is what the caller themselves just sent. There is no path to assets the account already holds, no approval, no delegatecall, and no storage write. Note the previous pass reached SAFE by a mistaken route (it inspected the delegate contract's own slot 0, which is not the storage that executes under delegation); the conclusion survives for a stronger reason than the one it gave.</t>
+        </is>
+      </c>
+      <c r="AD21" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AE21" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AF21" s="12" t="inlineStr">
+        <is>
+          <t>166-byte runtime on base exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Instruction census (whole contract): CALL×1, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AG21" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AH21" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=166 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 0, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AI21" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) forwarding only msg.value to a fixed destination ([('&lt;no dispatcher recovered; analysed from pc=0&gt;', 87, 'stored(sload)')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
